--- a/Assets/Documents/Concepts/Cards by Layer.xlsx
+++ b/Assets/Documents/Concepts/Cards by Layer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willc\My Stuff\School\CSC 486C\Assets\Cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB32419F-7CCE-4B71-A28D-D6C1FBFFF560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E494A-AFA7-47A2-8BC1-811D6443AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attack" sheetId="10" r:id="rId1"/>
@@ -253,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -504,6 +504,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -17126,6 +17129,13 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT prst="angle"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -17197,6 +17207,13 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT prst="angle"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -17268,6 +17285,13 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT prst="angle"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -17340,6 +17364,13 @@
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="152400" h="50800" prst="softRound"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -17412,6 +17443,13 @@
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="152400" h="50800" prst="softRound"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -19477,6 +19515,13 @@
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="165100" prst="coolSlant"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="3">
@@ -19505,13 +19550,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>95248</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>109849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>798206</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>366740</xdr:rowOff>
@@ -19529,7 +19574,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15667757" y="414649"/>
+          <a:off x="21680630" y="414649"/>
           <a:ext cx="1090885" cy="1088164"/>
           <a:chOff x="7552765" y="1580029"/>
           <a:chExt cx="720000" cy="720000"/>
@@ -19786,13 +19831,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>179554</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>109849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>357407</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>409978</xdr:rowOff>
@@ -19810,7 +19855,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="20282499" y="414649"/>
+          <a:off x="26295372" y="414649"/>
           <a:ext cx="1549453" cy="1131402"/>
           <a:chOff x="7021203" y="1580029"/>
           <a:chExt cx="438150" cy="330299"/>
@@ -20083,6 +20128,13 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -20113,6 +20165,56 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>27710</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>3001</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{126394C9-BCE5-FC1E-BDE5-3A7FFD3821B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14159345" y="304800"/>
+          <a:ext cx="5818910" cy="7858528"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -20430,11 +20532,11 @@
       <c r="M3" s="64"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="2"/>
       <c r="AB3" s="64"/>
@@ -20452,11 +20554,11 @@
       <c r="M4" s="65"/>
       <c r="N4" s="63"/>
       <c r="O4" s="5"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="122"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="123"/>
+      <c r="V4" s="123"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="63"/>
       <c r="AB4" s="65"/>
@@ -20474,11 +20576,11 @@
       <c r="M5" s="66"/>
       <c r="N5" s="63"/>
       <c r="O5" s="5"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="122"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="63"/>
       <c r="AB5" s="65"/>
@@ -20496,11 +20598,11 @@
       <c r="M6" s="60"/>
       <c r="N6" s="61"/>
       <c r="O6" s="5"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
+      <c r="R6" s="123"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="123"/>
+      <c r="U6" s="123"/>
+      <c r="V6" s="123"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="78"/>
       <c r="AB6" s="78"/>
@@ -20518,11 +20620,11 @@
       <c r="M7" s="74"/>
       <c r="N7" s="74"/>
       <c r="O7" s="75"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="122"/>
-      <c r="V7" s="122"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="123"/>
+      <c r="U7" s="123"/>
+      <c r="V7" s="123"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="74"/>
       <c r="AB7" s="74"/>
@@ -20540,11 +20642,11 @@
       <c r="M8" s="72"/>
       <c r="N8" s="72"/>
       <c r="O8" s="7"/>
-      <c r="R8" s="122"/>
-      <c r="S8" s="122"/>
-      <c r="T8" s="122"/>
-      <c r="U8" s="122"/>
-      <c r="V8" s="122"/>
+      <c r="R8" s="123"/>
+      <c r="S8" s="123"/>
+      <c r="T8" s="123"/>
+      <c r="U8" s="123"/>
+      <c r="V8" s="123"/>
       <c r="Z8" s="6"/>
       <c r="AA8" s="72"/>
       <c r="AB8" s="72"/>
@@ -21375,7 +21477,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="C2:W9"/>
+  <dimension ref="C2:AD9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="1.6640625" customWidth="1"/>
@@ -21392,19 +21494,25 @@
     <col min="13" max="13" width="47.6640625" customWidth="1"/>
     <col min="14" max="14" width="12.6640625" customWidth="1"/>
     <col min="15" max="15" width="5.6640625" customWidth="1"/>
-    <col min="16" max="16" width="1.6640625" customWidth="1"/>
-    <col min="17" max="17" width="20.6640625" customWidth="1"/>
-    <col min="18" max="18" width="1.6640625" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" customWidth="1"/>
-    <col min="21" max="21" width="47.6640625" customWidth="1"/>
-    <col min="22" max="22" width="12.6640625" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" customWidth="1"/>
-    <col min="24" max="24" width="1.6640625" customWidth="1"/>
+    <col min="16" max="17" width="1.6640625" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" customWidth="1"/>
+    <col min="20" max="20" width="47.6640625" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" customWidth="1"/>
+    <col min="22" max="22" width="5.6640625" customWidth="1"/>
+    <col min="23" max="23" width="1.6640625" customWidth="1"/>
+    <col min="24" max="24" width="20.6640625" customWidth="1"/>
+    <col min="25" max="25" width="1.6640625" customWidth="1"/>
+    <col min="26" max="26" width="5.6640625" customWidth="1"/>
+    <col min="27" max="27" width="12.6640625" customWidth="1"/>
+    <col min="28" max="28" width="47.6640625" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" customWidth="1"/>
+    <col min="30" max="30" width="5.6640625" customWidth="1"/>
+    <col min="31" max="31" width="1.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:23" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:30" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="30"/>
       <c r="D3" s="31"/>
       <c r="E3" s="116"/>
@@ -21415,13 +21523,18 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="3"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="64"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="3"/>
     </row>
-    <row r="4" spans="3:23" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:30" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="33"/>
       <c r="D4" s="120"/>
       <c r="E4" s="117"/>
@@ -21432,13 +21545,18 @@
       <c r="M4" s="8"/>
       <c r="N4" s="63"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="5"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="5"/>
     </row>
-    <row r="5" spans="3:23" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:30" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="33"/>
       <c r="D5" s="120"/>
       <c r="E5" s="117"/>
@@ -21449,13 +21567,18 @@
       <c r="M5" s="8"/>
       <c r="N5" s="63"/>
       <c r="O5" s="5"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="5"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="122"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="122"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="5"/>
     </row>
-    <row r="6" spans="3:23" ht="288" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="3:30" ht="288" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" s="33"/>
       <c r="D6" s="121"/>
       <c r="E6" s="121"/>
@@ -21466,13 +21589,18 @@
       <c r="M6" s="112"/>
       <c r="N6" s="113"/>
       <c r="O6" s="5"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="5"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="122"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="78"/>
+      <c r="AB6" s="78"/>
+      <c r="AC6" s="78"/>
+      <c r="AD6" s="5"/>
     </row>
-    <row r="7" spans="3:23" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:30" ht="169.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="33"/>
       <c r="D7" s="118"/>
       <c r="E7" s="118"/>
@@ -21483,13 +21611,18 @@
       <c r="M7" s="114"/>
       <c r="N7" s="114"/>
       <c r="O7" s="5"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="75"/>
+      <c r="R7" s="122"/>
+      <c r="S7" s="122"/>
+      <c r="T7" s="122"/>
+      <c r="U7" s="122"/>
+      <c r="V7" s="122"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="74"/>
+      <c r="AB7" s="74"/>
+      <c r="AC7" s="74"/>
+      <c r="AD7" s="75"/>
     </row>
-    <row r="8" spans="3:23" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:30" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="35"/>
       <c r="D8" s="115"/>
       <c r="E8" s="115"/>
@@ -21500,27 +21633,33 @@
       <c r="M8" s="72"/>
       <c r="N8" s="72"/>
       <c r="O8" s="7"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="7"/>
+      <c r="R8" s="122"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
+      <c r="V8" s="122"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="72"/>
+      <c r="AB8" s="72"/>
+      <c r="AC8" s="72"/>
+      <c r="AD8" s="7"/>
     </row>
-    <row r="9" spans="3:23" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="3:30" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="T8:V8"/>
+  <mergeCells count="18">
+    <mergeCell ref="AA8:AC8"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="U3:U5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="R3:V8"/>
+    <mergeCell ref="AB3:AB5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AA6:AC6"/>
+    <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="L6:N6"/>

--- a/Assets/Documents/Concepts/Cards by Layer.xlsx
+++ b/Assets/Documents/Concepts/Cards by Layer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willc\My Stuff\School\CSC 486C\Assets\Cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4957ECB-70C4-4129-96E7-5BED47AB6B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B038B8-AB46-4F11-A598-2742BB4255FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -58,38 +58,25 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="2">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>FIREBALL</t>
   </si>
   <si>
     <t>Borders</t>
-  </si>
-  <si>
-    <t>Spark</t>
   </si>
   <si>
     <t>Card Name</t>
@@ -104,31 +91,13 @@
     <t>fizzles on walls, explodes on enemies, stun</t>
   </si>
   <si>
-    <t>Tidal Wave</t>
-  </si>
-  <si>
     <t>wave carries enemies to wall, deals damage continuously</t>
-  </si>
-  <si>
-    <t>Bramble Snare</t>
-  </si>
-  <si>
-    <t>Life Steal</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
     <t>Attack</t>
-  </si>
-  <si>
-    <t>Void Hole</t>
-  </si>
-  <si>
-    <t>Astral Dagger</t>
-  </si>
-  <si>
-    <t>Lightning Bolt</t>
   </si>
   <si>
     <t>Element</t>
@@ -160,12 +129,36 @@
   <si>
     <t>BG</t>
   </si>
+  <si>
+    <t>SPARK</t>
+  </si>
+  <si>
+    <t>TIDAL WAVE</t>
+  </si>
+  <si>
+    <t>BRAMBLE SNARE</t>
+  </si>
+  <si>
+    <t>LIFE STEAL</t>
+  </si>
+  <si>
+    <t>VOID HOLE</t>
+  </si>
+  <si>
+    <t>ASTRAL DAGGER</t>
+  </si>
+  <si>
+    <t>LIGHTNING BOLT</t>
+  </si>
+  <si>
+    <t>snare trap</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,8 +201,26 @@
       <name val="Germania One"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Germania One"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Germania One"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Germania One"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,6 +266,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -459,10 +482,15 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -473,23 +501,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -500,64 +516,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -584,47 +573,74 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -647,48 +663,151 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,13 +816,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFF9999"/>
       <color rgb="FFFF5050"/>
       <color rgb="FFDBCABD"/>
-      <color rgb="FFFF9999"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FF37343E"/>
       <color rgb="FFCC66FF"/>
-      <color rgb="FFFFFFCC"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFCCFFFF"/>
     </mruColors>
@@ -723,25 +842,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
+      <xdr:oneCellAnchor>
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
+        <xdr:ext cx="3705225" cy="5000625"/>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="6" name="Picture 5">
+            <xdr:cNvPr id="27" name="Picture 26">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C08EF5C-7B09-4374-8269-E9C60C2E4445}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10BFF7D7-A13C-4FB2-BD93-A1F224A81DBD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -749,7 +863,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6161"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6210"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -763,127 +877,7 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="609600" y="190500"/>
-              <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="7" name="Picture 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAF909A7-E781-4A2E-9198-CE439B7C1AEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6162"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="609600" y="190500"/>
-              <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="8" name="Picture 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EABE02CC-9FE9-48A4-8B48-88209E4289F7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6163"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="609600" y="190500"/>
+              <a:off x="609600" y="200025"/>
               <a:ext cx="3705225" cy="5000625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -918,10 +912,10 @@
         <xdr:ext cx="3705225" cy="5000625"/>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="9" name="Picture 8">
+            <xdr:cNvPr id="36" name="Picture 35">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1456823-1886-4E68-AF4B-F4421CA43454}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A02927B-C011-4EC0-9E4A-58473AD3A385}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -929,7 +923,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6164"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6211"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -943,128 +937,8 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="609600" y="190500"/>
+              <a:off x="4914900" y="200025"/>
               <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="10" name="Picture 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C78D783E-CDDF-42F9-983A-7124AC9A68BF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6165"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="612321" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="11" name="Picture 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2A6D250-384A-4A34-AE58-EE7A05BB79D4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6166"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="612321" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1095,13 +969,13 @@
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
+        <xdr:ext cx="3705225" cy="5000625"/>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="12" name="Picture 11">
+            <xdr:cNvPr id="43" name="Picture 42">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86EC0562-E30E-45C5-9194-8EE3627D64BF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D49876F9-CA72-4739-9587-40780CF67CDB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1109,7 +983,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6167"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6212"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1123,127 +997,7 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="612321" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="13" name="Picture 12">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE67D67F-5F02-4665-B1FE-FFA4A6B4C752}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6168"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="612321" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="14" name="Picture 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6550CD81-45B9-4ACE-9C2F-F46AD67393D6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6169"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="4925786" y="190500"/>
+              <a:off x="9220200" y="200025"/>
               <a:ext cx="3705225" cy="5000625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1270,18 +1024,18 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:oneCellAnchor>
         <xdr:from>
-          <xdr:col>5</xdr:col>
+          <xdr:col>19</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:ext cx="3705225" cy="5000625"/>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="15" name="Picture 14">
+            <xdr:cNvPr id="44" name="Picture 43">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45158EE0-602C-431E-9129-0BE541F34618}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C537AE-AE63-47AB-A05E-DA2606D35733}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1289,7 +1043,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6170"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6213"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1303,248 +1057,8 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="9239250" y="190500"/>
+              <a:off x="13525500" y="200025"/>
               <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="16" name="Picture 15">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEA52CEB-0803-4C46-84B6-0A04D19A5E5F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6171"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="13552714" y="190500"/>
-              <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="17" name="Picture 16">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{228F9928-6813-44D2-99DD-6C3C512C41B1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6172"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="17866179" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="18" name="Picture 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7AA7B2A-46BB-46C9-AE48-75BE8E2CB66F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6173"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="22179643" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3710668" cy="5003346"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="19" name="Picture 18">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EAB619A-94C0-40AB-8662-7C0C56C0C5F1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6174"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="26493107" y="190500"/>
-              <a:ext cx="3710668" cy="5003346"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13146,17 +12660,13 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
     <v>0</v>
     <v>5</v>
   </rv>
   <rv s="0">
     <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -13175,7 +12685,6 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -13445,66 +12954,175 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="B2:N4"/>
+  <dimension ref="B1:X8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="55.42578125" customWidth="1"/>
-    <col min="4" max="4" width="55.42578125" customWidth="1"/>
-    <col min="6" max="6" width="55.42578125" customWidth="1"/>
-    <col min="8" max="8" width="55.42578125" customWidth="1"/>
-    <col min="10" max="10" width="55.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.42578125" customWidth="1"/>
-    <col min="14" max="14" width="55.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="4" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" customWidth="1"/>
+    <col min="16" max="16" width="25.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" customWidth="1"/>
+    <col min="18" max="18" width="4" customWidth="1"/>
+    <col min="20" max="20" width="4" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="25.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" customWidth="1"/>
+    <col min="24" max="24" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="393" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" t="e" vm="1">
-        <v>#VALUE!</v>
+    <row r="1" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="131"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="141"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="154"/>
+      <c r="R2" s="155"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="167"/>
+    </row>
+    <row r="3" spans="2:24" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="132"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129" t="str">
+        <f>Src!$A5</f>
+        <v>FIREBALL</v>
       </c>
-      <c r="D2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="E3" s="129"/>
+      <c r="F3" s="133"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143" t="str">
+        <f>Src!A6</f>
+        <v>SPARK</v>
       </c>
-      <c r="F2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="K3" s="143"/>
+      <c r="L3" s="144"/>
+      <c r="N3" s="156"/>
+      <c r="O3" s="157"/>
+      <c r="P3" s="177" t="str">
+        <f>Src!A7</f>
+        <v>TIDAL WAVE</v>
       </c>
-      <c r="H2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="Q3" s="157"/>
+      <c r="R3" s="158"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169"/>
+      <c r="V3" s="178" t="str">
+        <f>Src!A8</f>
+        <v>BRAMBLE SNARE</v>
       </c>
-      <c r="J2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="W3" s="169"/>
+      <c r="X3" s="170"/>
+    </row>
+    <row r="4" spans="2:24" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="134"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="147"/>
+      <c r="N4" s="159"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="160"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="161"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="171"/>
+      <c r="V4" s="171"/>
+      <c r="W4" s="171"/>
+      <c r="X4" s="172"/>
+    </row>
+    <row r="5" spans="2:24" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="12"/>
+      <c r="C5" s="138" t="str">
+        <f>Src!$C5</f>
+        <v>explodes on anything, burn DOT</v>
       </c>
-      <c r="L2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="135"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="148" t="str">
+        <f>Src!$C6</f>
+        <v>fizzles on walls, explodes on enemies, stun</v>
       </c>
-      <c r="N2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="149"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="162" t="str">
+        <f>Src!C7</f>
+        <v>wave carries enemies to wall, deals damage continuously</v>
       </c>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="162"/>
+      <c r="R5" s="163"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="173" t="str">
+        <f>Src!C8</f>
+        <v>snare trap</v>
+      </c>
+      <c r="V5" s="173"/>
+      <c r="W5" s="173"/>
+      <c r="X5" s="174"/>
     </row>
-    <row r="3" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:14" ht="393" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+    <row r="6" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="14"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="137"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="151"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="152"/>
+      <c r="N6" s="164"/>
+      <c r="O6" s="165"/>
+      <c r="P6" s="165"/>
+      <c r="Q6" s="165"/>
+      <c r="R6" s="166"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="175"/>
+      <c r="V6" s="175"/>
+      <c r="W6" s="175"/>
+      <c r="X6" s="176"/>
     </row>
+    <row r="7" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:24" ht="393" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="U5:W5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -13522,144 +13140,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="E1" s="122" t="s">
-        <v>25</v>
+      <c r="C1" s="58"/>
+      <c r="E1" s="58" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="393" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="e" vm="2">
+      <c r="A2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E2" t="e" vm="3">
+      <c r="E2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="124" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" s="126" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="125" t="s">
+    <row r="3" spans="1:5" s="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" s="61" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="125" t="s">
-        <v>11</v>
+      <c r="D4" s="60" t="s">
+        <v>9</v>
       </c>
-      <c r="C4" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="125"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13694,147 +13315,153 @@
     <row r="3" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="68"/>
+      <c r="E3" s="125" t="str">
+        <f>Src!A5</f>
+        <v>FIREBALL</v>
+      </c>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="128"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="128"/>
-      <c r="O3" s="130"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="12"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="72"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="111"/>
       <c r="G4" s="13"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="134"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="12"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="72"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="111"/>
       <c r="G5" s="13"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="134"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="12"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
       <c r="G6" s="13"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
-      <c r="O6" s="134"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="12"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="137"/>
+      <c r="D7" s="128" t="str">
+        <f>Src!C5</f>
+        <v>explodes on anything, burn DOT</v>
+      </c>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="127"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="79"/>
     </row>
     <row r="8" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="14"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
       <c r="G8" s="15"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="140"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="3:15" ht="10.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="80"/>
+      <c r="E12" s="105"/>
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
       <c r="K12" s="1"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="69"/>
+      <c r="M12" s="68"/>
       <c r="N12" s="2"/>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="19"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="78"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="20"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="58"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="67"/>
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="19"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="78"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="103"/>
       <c r="G14" s="20"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="58"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="67"/>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="19"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
       <c r="G15" s="20"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="19"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="77"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="102"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="67"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="79"/>
     </row>
     <row r="17" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="21"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
       <c r="G17" s="22"/>
       <c r="K17" s="6"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
+      <c r="N17" s="76"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13842,73 +13469,73 @@
     <row r="21" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="87"/>
+      <c r="E21" s="91"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25"/>
       <c r="K21" s="1"/>
       <c r="L21" s="2"/>
-      <c r="M21" s="69"/>
+      <c r="M21" s="68"/>
       <c r="N21" s="2"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="26"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="86"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="90"/>
       <c r="G22" s="27"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="58"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="67"/>
       <c r="O22" s="5"/>
     </row>
     <row r="23" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="26"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="86"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="90"/>
       <c r="G23" s="27"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="58"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="67"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="26"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
       <c r="G24" s="27"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="26"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="98"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="67"/>
+      <c r="L25" s="78"/>
+      <c r="M25" s="78"/>
+      <c r="N25" s="78"/>
+      <c r="O25" s="79"/>
     </row>
     <row r="26" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="28"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
       <c r="G26" s="29"/>
       <c r="K26" s="6"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76"/>
+      <c r="N26" s="76"/>
       <c r="O26" s="7"/>
     </row>
     <row r="27" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13916,73 +13543,73 @@
     <row r="30" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="37"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="98"/>
+      <c r="E30" s="88"/>
       <c r="F30" s="38"/>
       <c r="G30" s="39"/>
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="69"/>
+      <c r="M30" s="68"/>
       <c r="N30" s="2"/>
       <c r="O30" s="3"/>
     </row>
     <row r="31" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="40"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="92"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="82"/>
       <c r="G31" s="41"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="58"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="67"/>
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="40"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="92"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="82"/>
       <c r="G32" s="41"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="58"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="67"/>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="40"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
       <c r="G33" s="41"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="61"/>
-      <c r="N33" s="62"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="65"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="40"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="91"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="95"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="66"/>
-      <c r="M34" s="66"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="67"/>
+      <c r="L34" s="78"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="78"/>
+      <c r="O34" s="79"/>
     </row>
     <row r="35" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="42"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="93"/>
       <c r="G35" s="43"/>
       <c r="K35" s="6"/>
-      <c r="L35" s="74"/>
-      <c r="M35" s="74"/>
-      <c r="N35" s="74"/>
+      <c r="L35" s="76"/>
+      <c r="M35" s="76"/>
+      <c r="N35" s="76"/>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13990,73 +13617,73 @@
     <row r="39" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="44"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="101"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="45"/>
       <c r="G39" s="46"/>
       <c r="K39" s="1"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="69"/>
+      <c r="M39" s="68"/>
       <c r="N39" s="2"/>
       <c r="O39" s="3"/>
     </row>
     <row r="40" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="47"/>
-      <c r="D40" s="100"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="100"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="73"/>
       <c r="G40" s="48"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="58"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="69"/>
+      <c r="N40" s="67"/>
       <c r="O40" s="5"/>
     </row>
     <row r="41" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="47"/>
-      <c r="D41" s="100"/>
-      <c r="E41" s="102"/>
-      <c r="F41" s="100"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="73"/>
       <c r="G41" s="48"/>
       <c r="K41" s="4"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="58"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="67"/>
       <c r="O41" s="5"/>
     </row>
     <row r="42" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="47"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="96"/>
-      <c r="F42" s="96"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
       <c r="G42" s="48"/>
       <c r="K42" s="4"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="62"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="64"/>
+      <c r="N42" s="65"/>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="47"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="94"/>
-      <c r="F43" s="94"/>
-      <c r="G43" s="95"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="85"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
-      <c r="N43" s="66"/>
-      <c r="O43" s="67"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="79"/>
     </row>
     <row r="44" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C44" s="49"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
-      <c r="F44" s="93"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
       <c r="G44" s="50"/>
       <c r="K44" s="6"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="74"/>
-      <c r="N44" s="74"/>
+      <c r="L44" s="76"/>
+      <c r="M44" s="76"/>
+      <c r="N44" s="76"/>
       <c r="O44" s="7"/>
     </row>
     <row r="45" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14064,110 +13691,102 @@
     <row r="48" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="51"/>
       <c r="D48" s="52"/>
-      <c r="E48" s="108"/>
+      <c r="E48" s="71"/>
       <c r="F48" s="52"/>
       <c r="G48" s="53"/>
       <c r="K48" s="1"/>
       <c r="L48" s="2"/>
-      <c r="M48" s="69"/>
+      <c r="M48" s="68"/>
       <c r="N48" s="2"/>
       <c r="O48" s="3"/>
     </row>
     <row r="49" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="54"/>
-      <c r="D49" s="106"/>
-      <c r="E49" s="109"/>
-      <c r="F49" s="106"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="62"/>
       <c r="G49" s="55"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="58"/>
-      <c r="M49" s="70"/>
-      <c r="N49" s="58"/>
+      <c r="L49" s="67"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="67"/>
       <c r="O49" s="5"/>
     </row>
     <row r="50" spans="3:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="54"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="109"/>
-      <c r="F50" s="106"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="62"/>
       <c r="G50" s="55"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="58"/>
-      <c r="M50" s="71"/>
-      <c r="N50" s="58"/>
+      <c r="L50" s="67"/>
+      <c r="M50" s="70"/>
+      <c r="N50" s="67"/>
       <c r="O50" s="5"/>
     </row>
     <row r="51" spans="3:15" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="54"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
       <c r="G51" s="55"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="61"/>
-      <c r="N51" s="62"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
       <c r="O51" s="5"/>
     </row>
     <row r="52" spans="3:15" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="54"/>
-      <c r="D52" s="104"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="105"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="81"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="66"/>
-      <c r="M52" s="66"/>
-      <c r="N52" s="66"/>
-      <c r="O52" s="67"/>
+      <c r="L52" s="78"/>
+      <c r="M52" s="78"/>
+      <c r="N52" s="78"/>
+      <c r="O52" s="79"/>
     </row>
     <row r="53" spans="3:15" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C53" s="56"/>
-      <c r="D53" s="103"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="103"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
       <c r="G53" s="57"/>
       <c r="K53" s="6"/>
-      <c r="L53" s="74"/>
-      <c r="M53" s="74"/>
-      <c r="N53" s="74"/>
+      <c r="L53" s="76"/>
+      <c r="M53" s="76"/>
+      <c r="N53" s="76"/>
       <c r="O53" s="7"/>
     </row>
     <row r="54" spans="3:15" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="L51:N51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="M48:M50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="E48:E50"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="L53:N53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="L52:O52"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="M39:M41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="L43:O43"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="M12:M14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="D22:D23"/>
@@ -14184,30 +13803,38 @@
     <mergeCell ref="D25:G25"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="D24:F24"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="M12:M14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="L43:O43"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="L53:N53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="L52:O52"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="M39:M41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="M48:M50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="E48:E50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14255,7 +13882,7 @@
     <row r="3" spans="3:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="30"/>
       <c r="D3" s="31"/>
-      <c r="E3" s="115"/>
+      <c r="E3" s="114"/>
       <c r="F3" s="31"/>
       <c r="G3" s="32"/>
       <c r="K3" s="1"/>
@@ -14263,136 +13890,130 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="121"/>
-      <c r="T3" s="121"/>
-      <c r="U3" s="121"/>
-      <c r="V3" s="121"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+      <c r="T3" s="124"/>
+      <c r="U3" s="124"/>
+      <c r="V3" s="124"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="2"/>
-      <c r="AB3" s="69"/>
+      <c r="AB3" s="68"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="3"/>
     </row>
     <row r="4" spans="3:30" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="119"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="118"/>
       <c r="G4" s="34"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="58"/>
+      <c r="L4" s="67"/>
       <c r="M4" s="8"/>
-      <c r="N4" s="58"/>
+      <c r="N4" s="67"/>
       <c r="O4" s="5"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
       <c r="Z4" s="4"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="70"/>
-      <c r="AC4" s="58"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="69"/>
+      <c r="AC4" s="67"/>
       <c r="AD4" s="5"/>
     </row>
     <row r="5" spans="3:30" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="119"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="118"/>
       <c r="G5" s="34"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="58"/>
+      <c r="L5" s="67"/>
       <c r="M5" s="8"/>
-      <c r="N5" s="58"/>
+      <c r="N5" s="67"/>
       <c r="O5" s="5"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="121"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
       <c r="Z5" s="4"/>
-      <c r="AA5" s="58"/>
-      <c r="AB5" s="70"/>
-      <c r="AC5" s="58"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="69"/>
+      <c r="AC5" s="67"/>
       <c r="AD5" s="5"/>
     </row>
     <row r="6" spans="3:30" ht="288" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="33"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
       <c r="G6" s="34"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="112"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="122"/>
       <c r="O6" s="5"/>
-      <c r="R6" s="121"/>
-      <c r="S6" s="121"/>
-      <c r="T6" s="121"/>
-      <c r="U6" s="121"/>
-      <c r="V6" s="121"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
       <c r="Z6" s="4"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
       <c r="AD6" s="5"/>
     </row>
     <row r="7" spans="3:30" ht="169.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="33"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="118"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="117"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="113"/>
-      <c r="M7" s="113"/>
-      <c r="N7" s="113"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
       <c r="O7" s="5"/>
-      <c r="R7" s="121"/>
-      <c r="S7" s="121"/>
-      <c r="T7" s="121"/>
-      <c r="U7" s="121"/>
-      <c r="V7" s="121"/>
+      <c r="R7" s="124"/>
+      <c r="S7" s="124"/>
+      <c r="T7" s="124"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="124"/>
       <c r="Z7" s="4"/>
-      <c r="AA7" s="66"/>
-      <c r="AB7" s="66"/>
-      <c r="AC7" s="66"/>
-      <c r="AD7" s="67"/>
+      <c r="AA7" s="78"/>
+      <c r="AB7" s="78"/>
+      <c r="AC7" s="78"/>
+      <c r="AD7" s="79"/>
     </row>
     <row r="8" spans="3:30" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="35"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
       <c r="G8" s="36"/>
       <c r="K8" s="6"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
       <c r="O8" s="7"/>
-      <c r="R8" s="121"/>
-      <c r="S8" s="121"/>
-      <c r="T8" s="121"/>
-      <c r="U8" s="121"/>
-      <c r="V8" s="121"/>
+      <c r="R8" s="124"/>
+      <c r="S8" s="124"/>
+      <c r="T8" s="124"/>
+      <c r="U8" s="124"/>
+      <c r="V8" s="124"/>
       <c r="Z8" s="6"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="74"/>
+      <c r="AA8" s="76"/>
+      <c r="AB8" s="76"/>
+      <c r="AC8" s="76"/>
       <c r="AD8" s="7"/>
     </row>
     <row r="9" spans="3:30" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D6:F6"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="L8:N8"/>
@@ -14405,6 +14026,12 @@
     <mergeCell ref="AA6:AC6"/>
     <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Assets/Documents/Concepts/Cards by Layer.xlsx
+++ b/Assets/Documents/Concepts/Cards by Layer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willc\My Stuff\School\CSC 486C\Assets\Cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B038B8-AB46-4F11-A598-2742BB4255FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904E3C4A-3EF6-4EDE-8AA4-1DF25D224FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -58,20 +58,50 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>FIREBALL</t>
   </si>
@@ -83,15 +113,6 @@
   </si>
   <si>
     <t>Card Description</t>
-  </si>
-  <si>
-    <t>explodes on anything, burn DOT</t>
-  </si>
-  <si>
-    <t>fizzles on walls, explodes on enemies, stun</t>
-  </si>
-  <si>
-    <t>wave carries enemies to wall, deals damage continuously</t>
   </si>
   <si>
     <t>Type</t>
@@ -151,7 +172,22 @@
     <t>LIGHTNING BOLT</t>
   </si>
   <si>
-    <t>snare trap</t>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>fizzles on walls, explodes on enemies, stun (temp)</t>
+  </si>
+  <si>
+    <t>wave carries enemies to wall, deals damage continuously (temp)</t>
+  </si>
+  <si>
+    <t>snare trap (temp)</t>
+  </si>
+  <si>
+    <t>Explodes on anything, Burn DOT (TEMP)</t>
   </si>
 </sst>
 </file>
@@ -220,7 +256,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +314,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7373"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -690,32 +732,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -808,6 +824,41 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,6 +867,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF7373"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FFFF9999"/>
       <color rgb="FFFF5050"/>
@@ -844,126 +896,6 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:oneCellAnchor>
         <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="27" name="Picture 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10BFF7D7-A13C-4FB2-BD93-A1F224A81DBD}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6210"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="609600" y="200025"/>
-              <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:ext cx="3705225" cy="5000625"/>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="36" name="Picture 35">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A02927B-C011-4EC0-9E4A-58473AD3A385}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6211"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="4914900" y="200025"/>
-              <a:ext cx="3705225" cy="5000625"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:oneCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
-        <xdr:from>
           <xdr:col>13</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>1</xdr:row>
@@ -983,7 +915,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6212"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6276"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1043,7 +975,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6213"/>
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6277"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1080,6 +1012,187 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="3705225" cy="5000625"/>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="45" name="Picture 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7630490-DC59-4F23-8658-0F3076BE9981}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              <a:extLst>
+                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6278"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="609600" y="200025"/>
+              <a:ext cx="3705225" cy="5000625"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="3705225" cy="5000625"/>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="47" name="Picture 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D695E693-B771-4408-9EFB-AC18466C02B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              <a:extLst>
+                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
+                  <a14:cameraTool cellRange="Src!$A$2" spid="_x0000_s6279"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="4914900" y="200025"/>
+              <a:ext cx="3705225" cy="5000625"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>876300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0184F374-B5BC-2FB0-6707-51453D214AAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="200025"/>
+          <a:ext cx="1038225" cy="1038225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -12660,13 +12773,25 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <rv s="0">
     <v>0</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
     <v>5</v>
   </rv>
   <rv s="0">
-    <v>1</v>
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>0</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -12685,6 +12810,8 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
 </richValueRels>
 </file>
 
@@ -12981,143 +13108,147 @@
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="131"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="141"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154"/>
-      <c r="P2" s="154"/>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="155"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="172"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="131"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="145"/>
       <c r="T2" s="23"/>
       <c r="U2" s="24"/>
       <c r="V2" s="24"/>
       <c r="W2" s="24"/>
-      <c r="X2" s="167"/>
+      <c r="X2" s="157"/>
     </row>
     <row r="3" spans="2:24" s="58" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="132"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129" t="str">
+      <c r="B3" s="173"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174" t="str">
         <f>Src!$A5</f>
         <v>FIREBALL</v>
       </c>
-      <c r="E3" s="129"/>
-      <c r="F3" s="133"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143" t="str">
+      <c r="E3" s="174"/>
+      <c r="F3" s="175"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133" t="str">
         <f>Src!A6</f>
         <v>SPARK</v>
       </c>
-      <c r="K3" s="143"/>
-      <c r="L3" s="144"/>
-      <c r="N3" s="156"/>
-      <c r="O3" s="157"/>
-      <c r="P3" s="177" t="str">
+      <c r="K3" s="133"/>
+      <c r="L3" s="134"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="147"/>
+      <c r="P3" s="167" t="str">
         <f>Src!A7</f>
         <v>TIDAL WAVE</v>
       </c>
-      <c r="Q3" s="157"/>
-      <c r="R3" s="158"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169"/>
-      <c r="V3" s="178" t="str">
+      <c r="Q3" s="147"/>
+      <c r="R3" s="148"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="159"/>
+      <c r="V3" s="168" t="str">
         <f>Src!A8</f>
         <v>BRAMBLE SNARE</v>
       </c>
-      <c r="W3" s="169"/>
-      <c r="X3" s="170"/>
+      <c r="W3" s="159"/>
+      <c r="X3" s="160"/>
     </row>
     <row r="4" spans="2:24" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="12"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="134"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
-      <c r="N4" s="159"/>
-      <c r="O4" s="160"/>
-      <c r="P4" s="160"/>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="161"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="177" t="e" vm="1">
+        <f>Src!F5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="177"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="178"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="137"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="150"/>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="150"/>
+      <c r="R4" s="151"/>
       <c r="T4" s="26"/>
-      <c r="U4" s="171"/>
-      <c r="V4" s="171"/>
-      <c r="W4" s="171"/>
-      <c r="X4" s="172"/>
+      <c r="U4" s="161"/>
+      <c r="V4" s="161"/>
+      <c r="W4" s="161"/>
+      <c r="X4" s="162"/>
     </row>
     <row r="5" spans="2:24" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="12"/>
-      <c r="C5" s="138" t="str">
+      <c r="B5" s="176"/>
+      <c r="C5" s="179" t="str">
         <f>Src!$C5</f>
-        <v>explodes on anything, burn DOT</v>
+        <v>Explodes on anything, Burn DOT (TEMP)</v>
       </c>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="135"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="148" t="str">
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="180"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="138" t="str">
         <f>Src!$C6</f>
-        <v>fizzles on walls, explodes on enemies, stun</v>
+        <v>fizzles on walls, explodes on enemies, stun (temp)</v>
       </c>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="149"/>
-      <c r="N5" s="159"/>
-      <c r="O5" s="162" t="str">
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="139"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="152" t="str">
         <f>Src!C7</f>
-        <v>wave carries enemies to wall, deals damage continuously</v>
+        <v>wave carries enemies to wall, deals damage continuously (temp)</v>
       </c>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="162"/>
-      <c r="R5" s="163"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="153"/>
       <c r="T5" s="26"/>
-      <c r="U5" s="173" t="str">
+      <c r="U5" s="163" t="str">
         <f>Src!C8</f>
-        <v>snare trap</v>
+        <v>snare trap (temp)</v>
       </c>
-      <c r="V5" s="173"/>
-      <c r="W5" s="173"/>
-      <c r="X5" s="174"/>
+      <c r="V5" s="163"/>
+      <c r="W5" s="163"/>
+      <c r="X5" s="164"/>
     </row>
     <row r="6" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="14"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="137"/>
-      <c r="H6" s="150"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="152"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="165"/>
-      <c r="P6" s="165"/>
-      <c r="Q6" s="165"/>
-      <c r="R6" s="166"/>
+      <c r="B6" s="181"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="183"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="141"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="142"/>
+      <c r="N6" s="154"/>
+      <c r="O6" s="155"/>
+      <c r="P6" s="155"/>
+      <c r="Q6" s="155"/>
+      <c r="R6" s="156"/>
       <c r="T6" s="28"/>
-      <c r="U6" s="175"/>
-      <c r="V6" s="175"/>
-      <c r="W6" s="175"/>
-      <c r="X6" s="176"/>
+      <c r="U6" s="165"/>
+      <c r="V6" s="165"/>
+      <c r="W6" s="165"/>
+      <c r="X6" s="166"/>
     </row>
     <row r="7" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:24" ht="393" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="O5:Q5"/>
@@ -13131,156 +13262,171 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AA5721-EBD9-4F1E-B70A-78151D63ED79}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.42578125" customWidth="1"/>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
     <col min="5" max="5" width="55.42578125" customWidth="1"/>
+    <col min="6" max="6" width="47.42578125" customWidth="1"/>
+    <col min="8" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="58"/>
       <c r="E1" s="58" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="393" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="G1" s="58" t="s">
+        <v>24</v>
       </c>
-      <c r="E2" t="e" vm="2">
+      <c r="H1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" s="61" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="393" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:8" s="61" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="61" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="60"/>
+      <c r="F5" s="61" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="169" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="169" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="169" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="169" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="169" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="169" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="169" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="60"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>0</v>
+    <row r="8" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="169" t="s">
+        <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
+      <c r="B8" s="169" t="s">
+        <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>4</v>
+      <c r="C8" s="169" t="s">
+        <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D8" s="169" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="9" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B9" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D9" s="169" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="10" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
+      <c r="B10" s="169" t="s">
+        <v>5</v>
       </c>
-      <c r="C7" t="s">
-        <v>6</v>
+      <c r="D10" s="169" t="s">
+        <v>11</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="11" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="169" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="169" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="169" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
+    <row r="12" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="169" t="s">
+        <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B12" s="169" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="169" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E12" s="169" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
+    <row r="13" spans="1:8" s="169" customFormat="1" ht="186" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="169" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13367,7 +13513,7 @@
       <c r="C7" s="12"/>
       <c r="D7" s="128" t="str">
         <f>Src!C5</f>
-        <v>explodes on anything, burn DOT</v>
+        <v>Explodes on anything, Burn DOT (TEMP)</v>
       </c>
       <c r="E7" s="128"/>
       <c r="F7" s="128"/>
